--- a/Softball/postplanner-imports/ils-postplanner-tobi-2026-04-04.xlsx
+++ b/Softball/postplanner-imports/ils-postplanner-tobi-2026-04-04.xlsx
@@ -478,7 +478,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>04/04/2026  17:15</t>
+          <t>04/04/2026  18:31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>04/04/2026  17:30</t>
+          <t>04/04/2026  18:46</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -517,7 +517,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>04/04/2026  17:45</t>
+          <t>04/04/2026  19:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -538,7 +538,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>04/04/2026  18:15</t>
+          <t>04/04/2026  19:31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -557,7 +557,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>04/04/2026  18:30</t>
+          <t>04/04/2026  19:46</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -578,7 +578,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>04/04/2026  19:00</t>
+          <t>04/04/2026  20:16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -598,7 +598,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>04/04/2026  19:30</t>
+          <t>04/04/2026  20:46</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>04/04/2026  19:45</t>
+          <t>04/04/2026  21:01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>04/04/2026  20:00</t>
+          <t>04/04/2026  21:16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -658,7 +658,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>04/04/2026  20:30</t>
+          <t>04/04/2026  21:46</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -678,7 +678,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>04/04/2026  20:45</t>
+          <t>04/04/2026  22:01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>04/04/2026  21:15</t>
+          <t>04/04/2026  22:31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -720,7 +720,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04/04/2026  21:30</t>
+          <t>04/04/2026  22:46</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04/04/2026  21:45</t>
+          <t>04/04/2026  23:01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -763,7 +763,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04/04/2026  22:15</t>
+          <t>04/04/2026  23:31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -784,7 +784,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04/04/2026  22:30</t>
+          <t>04/04/2026  23:46</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
